--- a/Redimensionnement_41_SAV_PROD.xlsx
+++ b/Redimensionnement_41_SAV_PROD.xlsx
@@ -1753,12 +1753,12 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
-          <t>− 43 / semaine</t>
+          <t>− 37 / semaine</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C14" s="42" t="inlineStr">
         <is>
-          <t>Oui : ≈ 48 interventions récupérées</t>
+          <t>Oui : ≈ 40 interventions récupérées</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t>60 %</t>
+          <t>56 %</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t>≈ 90</t>
+          <t>≈ 77</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>≈ 149</t>
+          <t>≈ 137</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>Basculer sur le scénario B immédiatement : il ne coûte rien et fait passer le respect du J+1/J+2 de 3 à 12 secteurs. Ne déclencher le scénario C que si le volume SAV réel mesuré dépasse 90 interventions par semaine sur le département.</t>
+          <t>Basculer sur le scénario B immédiatement : il ne coûte rien et fait passer le respect du J+1/J+2 de 3 à 12 secteurs. Déclencher le scénario C si le volume SAV réel dépasse 78 interventions/semaine — ce qui est le cas si les 142 créneaux de la grille actuelle correspondent à des interventions réellement réalisées.</t>
         </is>
       </c>
       <c r="C21" s="25" t="n"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>Blois — référent SAV</t>
+          <t>100 % SAV — Blois + Valencisse</t>
         </is>
       </c>
       <c r="C7" s="35" t="n">
@@ -2331,155 +2331,155 @@
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
+          <t>Valencisse
+SAV 2</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>Blois
+SAV 4</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
           <t>Blois
 SAV 3</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="H7" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="G7" s="36" t="inlineStr">
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>Valencisse
+SAV 2</t>
+        </is>
+      </c>
+      <c r="J7" s="36" t="inlineStr">
+        <is>
+          <t>Blois
+SAV 4</t>
+        </is>
+      </c>
+      <c r="K7" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 3</t>
         </is>
       </c>
-      <c r="H7" s="36" t="inlineStr">
+      <c r="L7" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>Blois
-SAV 3</t>
-        </is>
-      </c>
-      <c r="J7" s="36" t="inlineStr">
+      <c r="M7" s="36" t="inlineStr">
+        <is>
+          <t>Valencisse
+SAV 2</t>
+        </is>
+      </c>
+      <c r="N7" s="37" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="O7" s="37" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="P7" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Blois — mixte SAV/PROD</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="K7" s="36" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>Blois
-SAV 3</t>
-        </is>
-      </c>
-      <c r="L7" s="36" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="G8" s="38" t="inlineStr">
         <is>
           <t>Blois
-SAV 3</t>
-        </is>
-      </c>
-      <c r="N7" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="O7" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="P7" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q7" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B8" s="28" t="inlineStr">
-        <is>
-          <t>Blois — mixte SAV/PROD</t>
-        </is>
-      </c>
-      <c r="C8" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="I8" s="38" t="inlineStr">
         <is>
           <t>Blois
 PROD 2</t>
         </is>
       </c>
-      <c r="F8" s="36" t="inlineStr">
+      <c r="J8" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="G8" s="38" t="inlineStr">
+      <c r="K8" s="38" t="inlineStr">
         <is>
           <t>Blois
 PROD 2</t>
         </is>
       </c>
-      <c r="H8" s="36" t="inlineStr">
+      <c r="L8" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="I8" s="38" t="inlineStr">
+      <c r="M8" s="38" t="inlineStr">
         <is>
           <t>Blois
 PROD 2</t>
         </is>
       </c>
-      <c r="J8" s="36" t="inlineStr">
+      <c r="N8" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="K8" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="L8" s="36" t="inlineStr">
-        <is>
-          <t>Blois
-SAV 4</t>
-        </is>
-      </c>
-      <c r="M8" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="N8" s="36" t="inlineStr">
-        <is>
-          <t>Blois
-SAV 4</t>
-        </is>
-      </c>
       <c r="O8" s="38" t="inlineStr">
         <is>
           <t>Blois
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t>Sud-Ouest — Pontlevoy / Valencisse</t>
+          <t>Sud-Ouest — Pontlevoy</t>
         </is>
       </c>
       <c r="C9" s="35" t="n">
@@ -2519,15 +2519,15 @@
 PROD 2</t>
         </is>
       </c>
-      <c r="F9" s="36" t="inlineStr">
-        <is>
-          <t>Valencisse
-SAV 3</t>
+      <c r="F9" s="38" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
         </is>
       </c>
       <c r="G9" s="38" t="inlineStr">
         <is>
-          <t>Valencisse
+          <t>Pontlevoy
 PROD 2</t>
         </is>
       </c>
@@ -2543,15 +2543,15 @@
 PROD 2</t>
         </is>
       </c>
-      <c r="J9" s="36" t="inlineStr">
-        <is>
-          <t>Valencisse
-SAV 3</t>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
         </is>
       </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>Valencisse
+          <t>Pontlevoy
 PROD 2</t>
         </is>
       </c>
@@ -2567,23 +2567,23 @@
 PROD 2</t>
         </is>
       </c>
-      <c r="N9" s="36" t="inlineStr">
-        <is>
-          <t>Valencisse
-SAV 3</t>
+      <c r="N9" s="38" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
         </is>
       </c>
       <c r="O9" s="38" t="inlineStr">
         <is>
-          <t>Valencisse
+          <t>Pontlevoy
 PROD 2</t>
         </is>
       </c>
       <c r="P9" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" s="35" t="n">
         <v>18</v>
-      </c>
-      <c r="Q9" s="35" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -3245,55 +3245,55 @@
       </c>
       <c r="D17" s="38" t="inlineStr">
         <is>
+          <t>Valencisse
+PROD 2</t>
+        </is>
+      </c>
+      <c r="E17" s="38" t="inlineStr">
+        <is>
           <t>Pontlevoy
 PROD 2</t>
         </is>
       </c>
-      <c r="E17" s="38" t="inlineStr">
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>Valencisse
+PROD 2</t>
+        </is>
+      </c>
+      <c r="G17" s="38" t="inlineStr">
         <is>
           <t>Pontlevoy
 PROD 2</t>
         </is>
       </c>
-      <c r="F17" s="38" t="inlineStr">
+      <c r="H17" s="38" t="inlineStr">
+        <is>
+          <t>Valencisse
+PROD 2</t>
+        </is>
+      </c>
+      <c r="I17" s="38" t="inlineStr">
         <is>
           <t>Pontlevoy
 PROD 2</t>
         </is>
       </c>
-      <c r="G17" s="38" t="inlineStr">
+      <c r="J17" s="38" t="inlineStr">
+        <is>
+          <t>Valencisse
+PROD 2</t>
+        </is>
+      </c>
+      <c r="K17" s="38" t="inlineStr">
         <is>
           <t>Pontlevoy
 PROD 2</t>
         </is>
       </c>
-      <c r="H17" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="I17" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="J17" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="K17" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
       <c r="L17" s="38" t="inlineStr">
         <is>
-          <t>Pontlevoy
+          <t>Valencisse
 PROD 2</t>
         </is>
       </c>
@@ -3411,7 +3411,7 @@
         <v>6</v>
       </c>
       <c r="D22" s="35" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -3466,18 +3466,18 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Mar · Jeu · Sam</t>
+          <t>Lun · Mer · Ven</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Ma-J-S</t>
+          <t>L-Me-V</t>
         </is>
       </c>
       <c r="F24" s="40">
@@ -4507,10 +4507,10 @@
         <v/>
       </c>
       <c r="N6" s="30" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P6" s="12">
         <f>$O6/$M6</f>
@@ -4579,10 +4579,10 @@
         <v/>
       </c>
       <c r="N7" s="30" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P7" s="12">
         <f>$O7/$M7</f>

--- a/Redimensionnement_41_SAV_PROD.xlsx
+++ b/Redimensionnement_41_SAV_PROD.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,13 +90,19 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00843C0C"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00843C0C"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="009C2E27"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -139,12 +145,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FBE5D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE5D6"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -158,7 +164,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -224,11 +230,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -354,7 +361,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1015,7 +1028,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -1024,7 +1037,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Part des créneaux SAV réservés réellement consommés. Curseur clé.</t>
+          <t>Le planning SAV fourni décrit un besoin ferme : 100 % des créneaux sont considérés comme consommés.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1077,7 @@
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -1073,7 +1086,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Effectif actuel déclaré</t>
+          <t>11 actuels + 2 de renfort — voir onglet Scénarios</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1097,7 @@
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -1093,7 +1106,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Déclaré — ce sont eux qui portent le rythme Mardi-Jeudi-Samedi</t>
+          <t>7 requis pour porter le rythme Ma-J-S — ce sont eux qui portent le rythme Mardi-Jeudi-Samedi</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1356,7 @@
       </c>
       <c r="B39" s="13" t="inlineStr"/>
       <c r="C39" s="13">
-        <f>'Grille SAV'!$D$34</f>
+        <f>'Grille SAV'!$D$36</f>
         <v/>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -1380,7 +1393,7 @@
         <f>$C$38-$C$40</f>
         <v/>
       </c>
-      <c r="D41" s="51">
+      <c r="D41" s="55">
         <f>"Seuil d'équilibre : "&amp;TEXT($C$38/$C$39,"0 %")&amp;" de remplissage des créneaux réservés, soit "&amp;TEXT($C$38,"0")&amp;" interventions SAV/semaine ("&amp;TEXT($C$38*4.3333,"0")&amp;"/mois)"</f>
         <v/>
       </c>
@@ -1616,17 +1629,17 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>A — Grille actuelle (capture)</t>
+          <t>A — Planning SAV fourni, à 11 techs</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>B — Rythme L-Me-V / Ma-J-S (RECOMMANDÉ)</t>
+          <t>B — 13 techniciens (RECOMMANDÉ)</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>C — Renfort +2 techniciens</t>
+          <t>C — 11 techniciens, SAV rationné</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1656,12 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>1 SAV pur + 5 référents mixtes + 5 PROD</t>
+          <t>1 SAV pur + 6 référents mixtes + 6 PROD</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1 SAV pur + 5 référents + 7 PROD</t>
+          <t>Idem B mais réservation SAV réduite</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1678,12 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1700,12 @@
       </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1717,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>3 sur 12 (Blois, Pontlevoy, Vendôme)</t>
+          <t>3 sur 12</t>
         </is>
       </c>
       <c r="C8" s="42" t="inlineStr">
@@ -1721,12 +1734,12 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Passages SAV / semaine / secteur</t>
+          <t>Passages SAV /sem. /secteur</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>1 à 5 selon le secteur — Cormenon et Vouzon : 1 seul</t>
+          <t>1 à 5 — Cormenon et Vouzon : 1 seul</t>
         </is>
       </c>
       <c r="C9" s="42" t="inlineStr">
@@ -1736,29 +1749,29 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>3 à 4</t>
+          <t>3 minimum partout</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>Créneaux SAV réservés / semaine</t>
+          <t>Interventions SAV servies /sem.</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>142 (cible du planning fourni)</t>
         </is>
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>142 — la totalité de la cible</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>78 — 45 % de la cible non servie</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1788,12 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
           <t>148</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>192</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1832,12 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
+          <t>− 5 / semaine</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
           <t>− 37 / semaine</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>+ 7 / semaine</t>
         </is>
       </c>
     </row>
@@ -1841,112 +1854,112 @@
       </c>
       <c r="C14" s="42" t="inlineStr">
         <is>
-          <t>Oui : ≈ 40 interventions récupérées</t>
+          <t>Oui, marginalement</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Sans objet</t>
+          <t>Oui, mais au prix du SAV non servi</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="21" t="inlineStr">
         <is>
-          <t>Taux de remplissage SAV maximal</t>
+          <t>Charge de l'équipe</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>non tenable au-delà de ~20 %</t>
+          <t>119 % — intenable</t>
         </is>
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t>56 %</t>
+          <t>93 % — 5 j-tech de marge</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>100 %</t>
+          <t>100 % — aucune marge</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>Volume SAV absorbable / semaine</t>
+          <t>Distance max. matin → après-midi</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>≈ 30</t>
+          <t>46 km (Épiais → Cormenon)</t>
         </is>
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t>≈ 77</t>
+          <t>30 km (Montoire → Cormenon)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>≈ 137</t>
+          <t>30 km</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="21" t="inlineStr">
         <is>
-          <t>Distance max. matin → après-midi</t>
+          <t>Samedi utilisé</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>46 km (Épiais → Cormenon)</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t>30 km (Montoire → Cormenon)</t>
+          <t>Oui — 7 techniciens à 6 jours</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>30 km</t>
+          <t>Oui — 5 techniciens à 6 jours</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>Samedi utilisé</t>
+          <t>Coût</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>Oui — les 5 techniciens à 6 jours portent le rythme Ma-J-S</t>
+          <t>+ 2 salaires</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Marge en cas d'absence</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Nulle</t>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="54" t="inlineStr">
+        <is>
+          <t>RECOMMANDATION</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>Le planning SAV que vous avez fourni représente 142 interventions par semaine, soit 25 jours-technicien. Ajoutées aux 46,3 jours-technicien de PROD majorée, cela fait 71,3 jours-technicien par semaine, alors que 11 techniciens en produisent 60. Le scénario B (13 techniciens, dont 7 à 6 jours) est le seul qui serve à la fois le volume SAV visé et le délai J+5/J+7 en PROD. À effectif constant, le scénario C tient le délai partout mais ne sert que 78 des 142 interventions SAV attendues.</t>
         </is>
       </c>
       <c r="C19" s="42" t="inlineStr">
@@ -1990,7 +2003,7 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>Basculer sur le scénario B immédiatement : il ne coûte rien et fait passer le respect du J+1/J+2 de 3 à 12 secteurs. Déclencher le scénario C si le volume SAV réel dépasse 78 interventions/semaine — ce qui est le cas si les 142 créneaux de la grille actuelle correspondent à des interventions réellement réalisées.</t>
+          <t>Basculer sur le scénario B immédiatement : il ne coûte rien et fait passer le respect du J+1/J+2 de 3 à 12 secteurs. Ne déclencher le scénario C que si le volume SAV réel mesuré dépasse 90 interventions par semaine sur le département.</t>
         </is>
       </c>
       <c r="C21" s="25" t="n"/>
@@ -2172,7 +2185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2321,7 +2334,7 @@
         </is>
       </c>
       <c r="C7" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
@@ -2331,70 +2344,72 @@
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
+          <t>Blois
+SAV 3</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>Blois
+SAV 4</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
           <t>Valencisse
 SAV 2</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="H7" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="G7" s="36" t="inlineStr">
+      <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 3</t>
         </is>
       </c>
-      <c r="H7" s="36" t="inlineStr">
+      <c r="J7" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="I7" s="36" t="inlineStr">
+      <c r="K7" s="36" t="inlineStr">
         <is>
           <t>Valencisse
 SAV 2</t>
         </is>
       </c>
-      <c r="J7" s="36" t="inlineStr">
+      <c r="L7" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="K7" s="36" t="inlineStr">
+      <c r="M7" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 3</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="N7" s="36" t="inlineStr">
         <is>
           <t>Blois
 SAV 4</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="O7" s="36" t="inlineStr">
         <is>
           <t>Valencisse
 SAV 2</t>
         </is>
       </c>
-      <c r="N7" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="O7" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
       <c r="P7" s="35" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="Q7" s="35" t="n">
         <v>0</v>
@@ -2408,89 +2423,89 @@
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
-          <t>Blois — mixte SAV/PROD</t>
+          <t>Blois — mixte SAV / PROD</t>
         </is>
       </c>
       <c r="C8" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Blois
-SAV 4</t>
-        </is>
-      </c>
-      <c r="E8" s="38" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="F8" s="36" t="inlineStr">
+SAV 3</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Blois
-SAV 4</t>
-        </is>
-      </c>
-      <c r="G8" s="38" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="G8" s="37" t="inlineStr">
         <is>
           <t>Blois
 PROD 2</t>
         </is>
       </c>
-      <c r="H8" s="36" t="inlineStr">
+      <c r="H8" s="37" t="inlineStr">
         <is>
           <t>Blois
-SAV 4</t>
-        </is>
-      </c>
-      <c r="I8" s="38" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
         <is>
           <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="J8" s="36" t="inlineStr">
+SAV 3</t>
+        </is>
+      </c>
+      <c r="J8" s="37" t="inlineStr">
         <is>
           <t>Blois
-SAV 4</t>
-        </is>
-      </c>
-      <c r="K8" s="38" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="K8" s="37" t="inlineStr">
         <is>
           <t>Blois
 PROD 2</t>
         </is>
       </c>
-      <c r="L8" s="36" t="inlineStr">
+      <c r="L8" s="37" t="inlineStr">
         <is>
           <t>Blois
-SAV 4</t>
-        </is>
-      </c>
-      <c r="M8" s="38" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="M8" s="36" t="inlineStr">
         <is>
           <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="N8" s="36" t="inlineStr">
+SAV 3</t>
+        </is>
+      </c>
+      <c r="N8" s="37" t="inlineStr">
         <is>
           <t>Blois
-SAV 4</t>
-        </is>
-      </c>
-      <c r="O8" s="38" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="O8" s="37" t="inlineStr">
         <is>
           <t>Blois
 PROD 2</t>
         </is>
       </c>
       <c r="P8" s="35" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Q8" s="35" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -2501,983 +2516,1105 @@
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
+          <t>Blois — PROD</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="H9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="I9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="J9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="K9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="L9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="M9" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="N9" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="O9" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="P9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Blois — PROD</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="H10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="I10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="J10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="K10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="L10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="M10" s="37" t="inlineStr">
+        <is>
+          <t>Blois
+PROD 2</t>
+        </is>
+      </c>
+      <c r="N10" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="O10" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="P10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
           <t>Sud-Ouest — Pontlevoy</t>
         </is>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>Pontlevoy
 SAV 3</t>
         </is>
       </c>
-      <c r="E9" s="38" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="F9" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="G9" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="H9" s="36" t="inlineStr">
+SAV 2</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>Pontlevoy
 SAV 3</t>
         </is>
       </c>
-      <c r="I9" s="38" t="inlineStr">
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>Pontlevoy
 PROD 2</t>
         </is>
       </c>
-      <c r="J9" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="K9" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="L9" s="36" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
         <is>
           <t>Pontlevoy
 SAV 3</t>
         </is>
       </c>
-      <c r="M9" s="38" t="inlineStr">
+      <c r="I11" s="36" t="inlineStr">
         <is>
           <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="N9" s="38" t="inlineStr">
+SAV 2</t>
+        </is>
+      </c>
+      <c r="J11" s="36" t="inlineStr">
         <is>
           <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="O9" s="38" t="inlineStr">
+SAV 3</t>
+        </is>
+      </c>
+      <c r="K11" s="37" t="inlineStr">
         <is>
           <t>Pontlevoy
 PROD 2</t>
         </is>
       </c>
-      <c r="P9" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q9" s="35" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B10" s="28" t="inlineStr">
-        <is>
-          <t>Nord — Vendômois / Perche / Beauce</t>
-        </is>
-      </c>
-      <c r="C10" s="35" t="n">
+      <c r="L11" s="36" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+SAV 3</t>
+        </is>
+      </c>
+      <c r="M11" s="36" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+SAV 2</t>
+        </is>
+      </c>
+      <c r="N11" s="36" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+SAV 3</t>
+        </is>
+      </c>
+      <c r="O11" s="37" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
+        </is>
+      </c>
+      <c r="P11" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Sud-Ouest — PROD Pontlevoy / Valencisse</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>Valencisse
+PROD 2</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
+        <is>
+          <t>Valencisse
+PROD 2</t>
+        </is>
+      </c>
+      <c r="H12" s="37" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
+        </is>
+      </c>
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
+        </is>
+      </c>
+      <c r="J12" s="37" t="inlineStr">
+        <is>
+          <t>Valencisse
+PROD 2</t>
+        </is>
+      </c>
+      <c r="K12" s="37" t="inlineStr">
+        <is>
+          <t>Valencisse
+PROD 2</t>
+        </is>
+      </c>
+      <c r="L12" s="37" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
+        </is>
+      </c>
+      <c r="M12" s="37" t="inlineStr">
+        <is>
+          <t>Pontlevoy
+PROD 2</t>
+        </is>
+      </c>
+      <c r="N12" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="O12" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="P12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Nord — Vendôme / Épiais</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Vendôme
 SAV 3</t>
         </is>
       </c>
-      <c r="E10" s="36" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>Épiais
 SAV 2</t>
         </is>
       </c>
-      <c r="F10" s="36" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
+        <is>
+          <t>Épiais
+SAV 3</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
+        <is>
+          <t>Épiais
+PROD 2</t>
+        </is>
+      </c>
+      <c r="H13" s="36" t="inlineStr">
+        <is>
+          <t>Vendôme
+SAV 3</t>
+        </is>
+      </c>
+      <c r="I13" s="36" t="inlineStr">
+        <is>
+          <t>Épiais
+SAV 2</t>
+        </is>
+      </c>
+      <c r="J13" s="36" t="inlineStr">
+        <is>
+          <t>Épiais
+SAV 3</t>
+        </is>
+      </c>
+      <c r="K13" s="37" t="inlineStr">
+        <is>
+          <t>Épiais
+PROD 2</t>
+        </is>
+      </c>
+      <c r="L13" s="36" t="inlineStr">
+        <is>
+          <t>Vendôme
+SAV 3</t>
+        </is>
+      </c>
+      <c r="M13" s="36" t="inlineStr">
+        <is>
+          <t>Épiais
+SAV 1</t>
+        </is>
+      </c>
+      <c r="N13" s="37" t="inlineStr">
+        <is>
+          <t>Épiais
+PROD 2</t>
+        </is>
+      </c>
+      <c r="O13" s="37" t="inlineStr">
+        <is>
+          <t>Épiais
+PROD 2</t>
+        </is>
+      </c>
+      <c r="P13" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q13" s="35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Nord — Montoire / Cormenon</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Montoire
+PROD 2</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>Montoire
+PROD 2</t>
+        </is>
+      </c>
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>Montoire
 SAV 3</t>
         </is>
       </c>
-      <c r="G10" s="36" t="inlineStr">
+      <c r="G14" s="36" t="inlineStr">
         <is>
           <t>Cormenon
 SAV 2</t>
         </is>
       </c>
-      <c r="H10" s="36" t="inlineStr">
-        <is>
-          <t>Vendôme
-SAV 3</t>
-        </is>
-      </c>
-      <c r="I10" s="36" t="inlineStr">
-        <is>
-          <t>Épiais
-SAV 2</t>
-        </is>
-      </c>
-      <c r="J10" s="36" t="inlineStr">
+      <c r="H14" s="37" t="inlineStr">
+        <is>
+          <t>Montoire
+PROD 2</t>
+        </is>
+      </c>
+      <c r="I14" s="37" t="inlineStr">
+        <is>
+          <t>Cormenon
+PROD 2</t>
+        </is>
+      </c>
+      <c r="J14" s="36" t="inlineStr">
         <is>
           <t>Montoire
 SAV 3</t>
         </is>
       </c>
-      <c r="K10" s="36" t="inlineStr">
+      <c r="K14" s="36" t="inlineStr">
         <is>
           <t>Cormenon
 SAV 2</t>
         </is>
       </c>
-      <c r="L10" s="36" t="inlineStr">
+      <c r="L14" s="37" t="inlineStr">
+        <is>
+          <t>Montoire
+PROD 2</t>
+        </is>
+      </c>
+      <c r="M14" s="37" t="inlineStr">
+        <is>
+          <t>Cormenon
+PROD 2</t>
+        </is>
+      </c>
+      <c r="N14" s="36" t="inlineStr">
+        <is>
+          <t>Montoire
+SAV 2</t>
+        </is>
+      </c>
+      <c r="O14" s="36" t="inlineStr">
+        <is>
+          <t>Cormenon
+SAV 3</t>
+        </is>
+      </c>
+      <c r="P14" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q14" s="35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Nord — PROD Vendômois / Beauce</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Vendôme
+PROD 2</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>Épiais
+PROD 2</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>Vendôme
+PROD 2</t>
+        </is>
+      </c>
+      <c r="G15" s="37" t="inlineStr">
+        <is>
+          <t>Épiais
+PROD 2</t>
+        </is>
+      </c>
+      <c r="H15" s="37" t="inlineStr">
+        <is>
+          <t>Vendôme
+PROD 2</t>
+        </is>
+      </c>
+      <c r="I15" s="37" t="inlineStr">
+        <is>
+          <t>Épiais
+PROD 2</t>
+        </is>
+      </c>
+      <c r="J15" s="37" t="inlineStr">
+        <is>
+          <t>Vendôme
+PROD 2</t>
+        </is>
+      </c>
+      <c r="K15" s="37" t="inlineStr">
+        <is>
+          <t>Épiais
+PROD 2</t>
+        </is>
+      </c>
+      <c r="L15" s="37" t="inlineStr">
+        <is>
+          <t>Vendôme
+PROD 2</t>
+        </is>
+      </c>
+      <c r="M15" s="37" t="inlineStr">
+        <is>
+          <t>Épiais
+PROD 2</t>
+        </is>
+      </c>
+      <c r="N15" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="O15" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="P15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Sologne Est — Crouy / Vouzon</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="36" t="inlineStr">
+        <is>
+          <t>Crouy-s-Cosson
 SAV 3</t>
         </is>
       </c>
-      <c r="M10" s="36" t="inlineStr">
-        <is>
-          <t>Épiais
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>Crouy-s-Cosson
+PROD 2</t>
+        </is>
+      </c>
+      <c r="F16" s="36" t="inlineStr">
+        <is>
+          <t>Vouzon
+SAV 3</t>
+        </is>
+      </c>
+      <c r="G16" s="37" t="inlineStr">
+        <is>
+          <t>Vouzon
+PROD 2</t>
+        </is>
+      </c>
+      <c r="H16" s="36" t="inlineStr">
+        <is>
+          <t>Crouy-s-Cosson
+SAV 3</t>
+        </is>
+      </c>
+      <c r="I16" s="37" t="inlineStr">
+        <is>
+          <t>Crouy-s-Cosson
+PROD 2</t>
+        </is>
+      </c>
+      <c r="J16" s="36" t="inlineStr">
+        <is>
+          <t>Vouzon
 SAV 2</t>
         </is>
       </c>
-      <c r="N10" s="36" t="inlineStr">
-        <is>
-          <t>Montoire
-SAV 3</t>
-        </is>
-      </c>
-      <c r="O10" s="36" t="inlineStr">
-        <is>
-          <t>Cormenon
+      <c r="K16" s="37" t="inlineStr">
+        <is>
+          <t>Vouzon
+PROD 2</t>
+        </is>
+      </c>
+      <c r="L16" s="36" t="inlineStr">
+        <is>
+          <t>Crouy-s-Cosson
 SAV 2</t>
         </is>
       </c>
-      <c r="P10" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q10" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
-        <is>
-          <t>Sologne Sud — Mur / Romorantin / La Ferté</t>
-        </is>
-      </c>
-      <c r="C11" s="35" t="n">
+      <c r="M16" s="37" t="inlineStr">
+        <is>
+          <t>Crouy-s-Cosson
+PROD 2</t>
+        </is>
+      </c>
+      <c r="N16" s="36" t="inlineStr">
+        <is>
+          <t>Vouzon
+SAV 2</t>
+        </is>
+      </c>
+      <c r="O16" s="37" t="inlineStr">
+        <is>
+          <t>Vouzon
+PROD 2</t>
+        </is>
+      </c>
+      <c r="P16" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q16" s="35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Sologne Sud — Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Mur-de-Sologne
 SAV 3</t>
         </is>
       </c>
-      <c r="E11" s="38" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>Mur-de-Sologne
 PROD 2</t>
         </is>
       </c>
-      <c r="F11" s="36" t="inlineStr">
+      <c r="F17" s="36" t="inlineStr">
         <is>
           <t>Romorantin
 SAV 3</t>
         </is>
       </c>
-      <c r="G11" s="36" t="inlineStr">
+      <c r="G17" s="36" t="inlineStr">
         <is>
           <t>La Ferté-Imb.
 SAV 2</t>
         </is>
       </c>
-      <c r="H11" s="36" t="inlineStr">
+      <c r="H17" s="36" t="inlineStr">
         <is>
           <t>Mur-de-Sologne
 SAV 3</t>
         </is>
       </c>
-      <c r="I11" s="38" t="inlineStr">
+      <c r="I17" s="36" t="inlineStr">
         <is>
           <t>Mur-de-Sologne
-PROD 2</t>
-        </is>
-      </c>
-      <c r="J11" s="36" t="inlineStr">
+SAV 1</t>
+        </is>
+      </c>
+      <c r="J17" s="36" t="inlineStr">
         <is>
           <t>Romorantin
-SAV 3</t>
-        </is>
-      </c>
-      <c r="K11" s="36" t="inlineStr">
+SAV 2</t>
+        </is>
+      </c>
+      <c r="K17" s="36" t="inlineStr">
         <is>
           <t>La Ferté-Imb.
-SAV 2</t>
-        </is>
-      </c>
-      <c r="L11" s="36" t="inlineStr">
+SAV 1</t>
+        </is>
+      </c>
+      <c r="L17" s="36" t="inlineStr">
         <is>
           <t>Mur-de-Sologne
 SAV 3</t>
         </is>
       </c>
-      <c r="M11" s="38" t="inlineStr">
+      <c r="M17" s="37" t="inlineStr">
         <is>
           <t>Mur-de-Sologne
 PROD 2</t>
         </is>
       </c>
-      <c r="N11" s="36" t="inlineStr">
+      <c r="N17" s="36" t="inlineStr">
         <is>
           <t>Romorantin
-SAV 3</t>
-        </is>
-      </c>
-      <c r="O11" s="36" t="inlineStr">
+SAV 1</t>
+        </is>
+      </c>
+      <c r="O17" s="36" t="inlineStr">
         <is>
           <t>La Ferté-Imb.
-SAV 2</t>
-        </is>
-      </c>
-      <c r="P11" s="35" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q11" s="35" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>Sologne Est — Crouy / Vouzon</t>
-        </is>
-      </c>
-      <c r="C12" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
+SAV 1</t>
+        </is>
+      </c>
+      <c r="P17" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Sologne — PROD</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>Romorantin
+PROD 2</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne
+PROD 2</t>
+        </is>
+      </c>
+      <c r="F18" s="37" t="inlineStr">
+        <is>
+          <t>Romorantin
+PROD 2</t>
+        </is>
+      </c>
+      <c r="G18" s="37" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne
+PROD 2</t>
+        </is>
+      </c>
+      <c r="H18" s="37" t="inlineStr">
+        <is>
+          <t>Romorantin
+PROD 2</t>
+        </is>
+      </c>
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne
+PROD 2</t>
+        </is>
+      </c>
+      <c r="J18" s="37" t="inlineStr">
+        <is>
+          <t>Romorantin
+PROD 2</t>
+        </is>
+      </c>
+      <c r="K18" s="37" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne
+PROD 2</t>
+        </is>
+      </c>
+      <c r="L18" s="37" t="inlineStr">
+        <is>
+          <t>Romorantin
+PROD 2</t>
+        </is>
+      </c>
+      <c r="M18" s="37" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne
+PROD 2</t>
+        </is>
+      </c>
+      <c r="N18" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="O18" s="38" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="P18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Sologne / Val de Loire — PROD</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>Crouy-s-Cosson
-SAV 3</t>
-        </is>
-      </c>
-      <c r="E12" s="38" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>Crouy-s-Cosson
 PROD 2</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne
+PROD 2</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="inlineStr">
+        <is>
+          <t>Romorantin
+PROD 2</t>
+        </is>
+      </c>
+      <c r="H19" s="37" t="inlineStr">
+        <is>
+          <t>Crouy-s-Cosson
+PROD 2</t>
+        </is>
+      </c>
+      <c r="I19" s="37" t="inlineStr">
+        <is>
+          <t>Crouy-s-Cosson
+PROD 2</t>
+        </is>
+      </c>
+      <c r="J19" s="37" t="inlineStr">
+        <is>
+          <t>Romorantin
+PROD 2</t>
+        </is>
+      </c>
+      <c r="K19" s="37" t="inlineStr">
+        <is>
+          <t>La Ferté-Imb.
+PROD 2</t>
+        </is>
+      </c>
+      <c r="L19" s="37" t="inlineStr">
         <is>
           <t>Vouzon
-SAV 3</t>
-        </is>
-      </c>
-      <c r="G12" s="38" t="inlineStr">
+PROD 2</t>
+        </is>
+      </c>
+      <c r="M19" s="37" t="inlineStr">
         <is>
           <t>Vouzon
 PROD 2</t>
         </is>
       </c>
-      <c r="H12" s="36" t="inlineStr">
-        <is>
-          <t>Crouy-s-Cosson
-SAV 3</t>
-        </is>
-      </c>
-      <c r="I12" s="38" t="inlineStr">
-        <is>
-          <t>Crouy-s-Cosson
-PROD 2</t>
-        </is>
-      </c>
-      <c r="J12" s="36" t="inlineStr">
-        <is>
-          <t>Vouzon
-SAV 3</t>
-        </is>
-      </c>
-      <c r="K12" s="38" t="inlineStr">
-        <is>
-          <t>Vouzon
-PROD 2</t>
-        </is>
-      </c>
-      <c r="L12" s="36" t="inlineStr">
-        <is>
-          <t>Crouy-s-Cosson
-SAV 3</t>
-        </is>
-      </c>
-      <c r="M12" s="38" t="inlineStr">
-        <is>
-          <t>Crouy-s-Cosson
-PROD 2</t>
-        </is>
-      </c>
-      <c r="N12" s="36" t="inlineStr">
-        <is>
-          <t>Vouzon
-SAV 3</t>
-        </is>
-      </c>
-      <c r="O12" s="38" t="inlineStr">
-        <is>
-          <t>Vouzon
-PROD 2</t>
-        </is>
-      </c>
-      <c r="P12" s="35" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q12" s="35" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>T7</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>PROD — Blois agglo</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="E13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="F13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="G13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="H13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="I13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="J13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="K13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="L13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="M13" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="N13" s="37" t="inlineStr">
+      <c r="N19" s="38" t="inlineStr">
         <is>
           <t>repos</t>
         </is>
       </c>
-      <c r="O13" s="37" t="inlineStr">
+      <c r="O19" s="38" t="inlineStr">
         <is>
           <t>repos</t>
         </is>
       </c>
-      <c r="P13" s="35" t="n">
+      <c r="P19" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="35" t="n">
+      <c r="Q19" s="35" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
-        <is>
-          <t>PROD — Blois agglo</t>
-        </is>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="E14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="F14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="G14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="H14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="I14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="J14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="K14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="L14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="M14" s="38" t="inlineStr">
-        <is>
-          <t>Blois
-PROD 2</t>
-        </is>
-      </c>
-      <c r="N14" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="O14" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="P14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="35" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>T9</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="inlineStr">
-        <is>
-          <t>PROD — Nord (Vendômois/Beauce)</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="38" t="inlineStr">
-        <is>
-          <t>Vendôme
-PROD 2</t>
-        </is>
-      </c>
-      <c r="E15" s="38" t="inlineStr">
-        <is>
-          <t>Épiais
-PROD 2</t>
-        </is>
-      </c>
-      <c r="F15" s="38" t="inlineStr">
-        <is>
-          <t>Vendôme
-PROD 2</t>
-        </is>
-      </c>
-      <c r="G15" s="38" t="inlineStr">
-        <is>
-          <t>Épiais
-PROD 2</t>
-        </is>
-      </c>
-      <c r="H15" s="38" t="inlineStr">
-        <is>
-          <t>Vendôme
-PROD 2</t>
-        </is>
-      </c>
-      <c r="I15" s="38" t="inlineStr">
-        <is>
-          <t>Épiais
-PROD 2</t>
-        </is>
-      </c>
-      <c r="J15" s="38" t="inlineStr">
-        <is>
-          <t>Vendôme
-PROD 2</t>
-        </is>
-      </c>
-      <c r="K15" s="38" t="inlineStr">
-        <is>
-          <t>Épiais
-PROD 2</t>
-        </is>
-      </c>
-      <c r="L15" s="38" t="inlineStr">
-        <is>
-          <t>Vendôme
-PROD 2</t>
-        </is>
-      </c>
-      <c r="M15" s="38" t="inlineStr">
-        <is>
-          <t>Épiais
-PROD 2</t>
-        </is>
-      </c>
-      <c r="N15" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="O15" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="P15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="35" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t>PROD — Sologne</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="38" t="inlineStr">
-        <is>
-          <t>Romorantin
-PROD 2</t>
-        </is>
-      </c>
-      <c r="E16" s="38" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne
-PROD 2</t>
-        </is>
-      </c>
-      <c r="F16" s="38" t="inlineStr">
-        <is>
-          <t>Romorantin
-PROD 2</t>
-        </is>
-      </c>
-      <c r="G16" s="38" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne
-PROD 2</t>
-        </is>
-      </c>
-      <c r="H16" s="38" t="inlineStr">
-        <is>
-          <t>Romorantin
-PROD 2</t>
-        </is>
-      </c>
-      <c r="I16" s="38" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne
-PROD 2</t>
-        </is>
-      </c>
-      <c r="J16" s="38" t="inlineStr">
-        <is>
-          <t>Romorantin
-PROD 2</t>
-        </is>
-      </c>
-      <c r="K16" s="38" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne
-PROD 2</t>
-        </is>
-      </c>
-      <c r="L16" s="38" t="inlineStr">
-        <is>
-          <t>Romorantin
-PROD 2</t>
-        </is>
-      </c>
-      <c r="M16" s="38" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne
-PROD 2</t>
-        </is>
-      </c>
-      <c r="N16" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="O16" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="P16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="35" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>T11</t>
-        </is>
-      </c>
-      <c r="B17" s="28" t="inlineStr">
-        <is>
-          <t>PROD — Sud-Ouest / Val de Cher</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="38" t="inlineStr">
-        <is>
-          <t>Valencisse
-PROD 2</t>
-        </is>
-      </c>
-      <c r="E17" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="F17" s="38" t="inlineStr">
-        <is>
-          <t>Valencisse
-PROD 2</t>
-        </is>
-      </c>
-      <c r="G17" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="H17" s="38" t="inlineStr">
-        <is>
-          <t>Valencisse
-PROD 2</t>
-        </is>
-      </c>
-      <c r="I17" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="J17" s="38" t="inlineStr">
-        <is>
-          <t>Valencisse
-PROD 2</t>
-        </is>
-      </c>
-      <c r="K17" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="L17" s="38" t="inlineStr">
-        <is>
-          <t>Valencisse
-PROD 2</t>
-        </is>
-      </c>
-      <c r="M17" s="38" t="inlineStr">
-        <is>
-          <t>Pontlevoy
-PROD 2</t>
-        </is>
-      </c>
-      <c r="N17" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="O17" s="37" t="inlineStr">
-        <is>
-          <t>repos</t>
-        </is>
-      </c>
-      <c r="P17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="35" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="27">
-        <f>SUM(C7:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="39" t="n"/>
-      <c r="E18" s="39" t="n"/>
-      <c r="F18" s="39" t="n"/>
-      <c r="G18" s="39" t="n"/>
-      <c r="H18" s="39" t="n"/>
-      <c r="I18" s="39" t="n"/>
-      <c r="J18" s="39" t="n"/>
-      <c r="K18" s="39" t="n"/>
-      <c r="L18" s="39" t="n"/>
-      <c r="M18" s="39" t="n"/>
-      <c r="N18" s="39" t="n"/>
-      <c r="O18" s="39" t="n"/>
-      <c r="P18" s="27">
-        <f>SUM(P7:P17)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="27">
-        <f>SUM(Q7:Q17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="27">
+        <f>SUM(C7:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="39" t="n"/>
+      <c r="H20" s="39" t="n"/>
+      <c r="I20" s="39" t="n"/>
+      <c r="J20" s="39" t="n"/>
+      <c r="K20" s="39" t="n"/>
+      <c r="L20" s="39" t="n"/>
+      <c r="M20" s="39" t="n"/>
+      <c r="N20" s="39" t="n"/>
+      <c r="O20" s="39" t="n"/>
+      <c r="P20" s="27">
+        <f>SUM(P7:P19)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="27">
+        <f>SUM(Q7:Q19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>CONTRÔLE DU DÉLAI SAV J+1 / J+2 — SECTEUR PAR SECTEUR</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Secteur</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>Jours de passage SAV</t>
         </is>
       </c>
-      <c r="C21" s="27" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>Passages /sem.</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Créneaux SAV réservés /sem.</t>
         </is>
       </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>Rythme</t>
         </is>
       </c>
-      <c r="F21" s="27" t="inlineStr">
+      <c r="F23" s="27" t="inlineStr">
         <is>
           <t>Délai SAV J+1/J+2</t>
         </is>
       </c>
-      <c r="G21" s="27" t="inlineStr">
+      <c r="G23" s="27" t="inlineStr">
         <is>
           <t>Charge SAV (j-tech/sem.)</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Lun · Mar · Mer · Jeu · Ven · Sam</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>50</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Quotidien</t>
-        </is>
-      </c>
-      <c r="F22" s="40">
-        <f>IF($C22&gt;=3,"OK","À CORRIGER")</f>
-        <v/>
-      </c>
-      <c r="G22" s="41">
-        <f>IFERROR($D22/INDEX('Demande 41'!$M$6:$M$17,MATCH($A22,'Demande 41'!$A$6:$A$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Pontlevoy</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Lun · Mer · Ven</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>L-Me-V</t>
-        </is>
-      </c>
-      <c r="F23" s="40">
-        <f>IF($C23&gt;=3,"OK","À CORRIGER")</f>
-        <v/>
-      </c>
-      <c r="G23" s="41">
-        <f>IFERROR($D23/INDEX('Demande 41'!$M$6:$M$17,MATCH($A23,'Demande 41'!$A$6:$A$17,0)),"")</f>
-        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>Valencisse</t>
+          <t>Blois</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Lun · Mer · Ven</t>
+          <t>Lun · Mar · Mer · Jeu · Ven · Sam</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D24" s="35" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>L-Me-V</t>
+          <t>Quotidien</t>
         </is>
       </c>
       <c r="F24" s="40">
@@ -3492,23 +3629,23 @@
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>Vendôme</t>
+          <t>Pontlevoy</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Lun · Mer · Ven</t>
+          <t>Lun · Mar · Mer · Jeu · Ven · Sam</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="35" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>L-Me-V</t>
+          <t>Quotidien</t>
         </is>
       </c>
       <c r="F25" s="40">
@@ -3523,12 +3660,12 @@
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>Épiais</t>
+          <t>Valencisse</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Lun · Mer · Ven</t>
+          <t>Mar · Jeu · Sam</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
@@ -3539,7 +3676,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>L-Me-V</t>
+          <t>Ma-J-S</t>
         </is>
       </c>
       <c r="F26" s="40">
@@ -3554,12 +3691,12 @@
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>Montoire-sur-le-Loir</t>
+          <t>Vendôme</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Mar · Jeu · Sam</t>
+          <t>Lun · Mer · Ven</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
@@ -3570,7 +3707,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Ma-J-S</t>
+          <t>L-Me-V</t>
         </is>
       </c>
       <c r="F27" s="40">
@@ -3585,23 +3722,23 @@
     <row r="28">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>Cormenon</t>
+          <t>Épiais</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Mar · Jeu · Sam</t>
+          <t>Lun · Mar · Mer · Jeu · Ven</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" s="35" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Ma-J-S</t>
+          <t>Quotidien</t>
         </is>
       </c>
       <c r="F28" s="40">
@@ -3616,23 +3753,23 @@
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>Crouy-sur-Cosson</t>
+          <t>Montoire-sur-le-Loir</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Lun · Mer · Ven</t>
+          <t>Mar · Jeu · Sam</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D29" s="35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>L-Me-V</t>
+          <t>Ma-J-S</t>
         </is>
       </c>
       <c r="F29" s="40">
@@ -3647,7 +3784,7 @@
     <row r="30">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>Vouzon</t>
+          <t>Cormenon</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -3659,7 +3796,7 @@
         <v>3</v>
       </c>
       <c r="D30" s="35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -3678,7 +3815,7 @@
     <row r="31">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>Mur-de-Sologne</t>
+          <t>Crouy-sur-Cosson</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -3690,7 +3827,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -3709,7 +3846,7 @@
     <row r="32">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>Romorantin-Lanthenay</t>
+          <t>Vouzon</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -3721,7 +3858,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -3740,23 +3877,23 @@
     <row r="33">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>La Ferté-Imbault</t>
+          <t>Mur-de-Sologne</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Mar · Jeu · Sam</t>
+          <t>Lun · Mer · Ven</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D33" s="35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Ma-J-S</t>
+          <t>L-Me-V</t>
         </is>
       </c>
       <c r="F33" s="40">
@@ -3769,45 +3906,107 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Mar · Jeu · Sam</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Ma-J-S</t>
+        </is>
+      </c>
+      <c r="F34" s="40">
+        <f>IF($C34&gt;=3,"OK","À CORRIGER")</f>
+        <v/>
+      </c>
+      <c r="G34" s="41">
+        <f>IFERROR($D34/INDEX('Demande 41'!$M$6:$M$17,MATCH($A34,'Demande 41'!$A$6:$A$17,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Mar · Jeu · Sam</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Ma-J-S</t>
+        </is>
+      </c>
+      <c r="F35" s="40">
+        <f>IF($C35&gt;=3,"OK","À CORRIGER")</f>
+        <v/>
+      </c>
+      <c r="G35" s="41">
+        <f>IFERROR($D35/INDEX('Demande 41'!$M$6:$M$17,MATCH($A35,'Demande 41'!$A$6:$A$17,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>12 secteurs</t>
         </is>
       </c>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27">
-        <f>SUM(D22:D33)</f>
-        <v/>
-      </c>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="33">
-        <f>SUM(G22:G33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Les 5 techniciens à 6 jours sont les 5 référents ruraux (T2 à T6) : c'est le samedi qui rend possible le rythme Mardi-Jeudi-Samedi, donc la tenue du J+1/J+2 sur la moitié des secteurs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Enchaînements matin → après-midi sur deux secteurs différents : Vendôme→Épiais 29 km · Montoire→Cormenon 30 km · Romorantin→La Ferté-Imbault 22 km. Tous les autres enchaînements restent dans le même secteur.</t>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27">
+        <f>SUM(D24:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="33">
+        <f>SUM(G24:G35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Fond orange dans l'onglet Effectif = les 7 techniciens à 6 jours. Ce sont eux qui portent les secteurs du rythme Mardi-Jeudi-Samedi : sans leur samedi, aucun créneau SAV n'existe à J+1/J+2 pour un appel du jeudi ou du vendredi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Enchaînements matin → après-midi sur deux secteurs différents : Montoire→Cormenon 30 km · Vendôme→Épiais 29 km · Romorantin→La Ferté-Imbault 22 km · Blois→Valencisse 11 km. Aucun enchaînement au-delà de 30 km.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -3820,7 +4019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3829,7 +4028,8 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3879,43 +4079,49 @@
       </c>
       <c r="G4" s="27" t="inlineStr">
         <is>
-          <t>Type de journée</t>
+          <t>SAV /sem.</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>PROD /sem.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>Référent SAV Blois</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
+        <is>
+          <t>100 % SAV — Blois + Valencisse</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Blois</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="D5" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="50" t="inlineStr">
         <is>
           <t>Blois</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="inlineStr">
-        <is>
-          <t>SAV toute la journée</t>
-        </is>
+      <c r="F5" s="50" t="inlineStr">
+        <is>
+          <t>Blois · Valencisse</t>
+        </is>
+      </c>
+      <c r="G5" s="46" t="n">
+        <v>39</v>
+      </c>
+      <c r="H5" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
@@ -3926,7 +4132,7 @@
       </c>
       <c r="B6" s="50" t="inlineStr">
         <is>
-          <t>Blois mixte</t>
+          <t>Blois — mixte SAV / PROD</t>
         </is>
       </c>
       <c r="C6" s="46" t="inlineStr">
@@ -3947,80 +4153,83 @@
           <t>Blois</t>
         </is>
       </c>
-      <c r="G6" s="50" t="inlineStr">
-        <is>
-          <t>SAV matin / PROD après-midi</t>
-        </is>
+      <c r="G6" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" s="46" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B7" s="50" t="inlineStr">
-        <is>
-          <t>Référent Sud-Ouest</t>
-        </is>
-      </c>
-      <c r="C7" s="46" t="inlineStr">
-        <is>
-          <t>Sud-Ouest</t>
-        </is>
-      </c>
-      <c r="D7" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="50" t="inlineStr">
-        <is>
-          <t>Pontlevoy ou Montrichard</t>
-        </is>
-      </c>
-      <c r="F7" s="50" t="inlineStr">
-        <is>
-          <t>Pontlevoy (L-Me-V) · Valencisse (Ma-J-S)</t>
-        </is>
-      </c>
-      <c r="G7" s="50" t="inlineStr">
-        <is>
-          <t>SAV matin / PROD après-midi</t>
-        </is>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Blois — PROD</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B8" s="50" t="inlineStr">
-        <is>
-          <t>Référent Nord</t>
-        </is>
-      </c>
-      <c r="C8" s="46" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="D8" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" s="50" t="inlineStr">
-        <is>
-          <t>Vendôme</t>
-        </is>
-      </c>
-      <c r="F8" s="50" t="inlineStr">
-        <is>
-          <t>Vendôme + Épiais (L-Me-V) · Montoire + Cormenon (Ma-J-S)</t>
-        </is>
-      </c>
-      <c r="G8" s="50" t="inlineStr">
-        <is>
-          <t>SAV matin et après-midi</t>
-        </is>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Blois — PROD</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -4031,12 +4240,12 @@
       </c>
       <c r="B9" s="50" t="inlineStr">
         <is>
-          <t>Référent Sologne Sud</t>
+          <t>Sud-Ouest — Pontlevoy</t>
         </is>
       </c>
       <c r="C9" s="46" t="inlineStr">
         <is>
-          <t>Sologne Sud</t>
+          <t>Sud-Ouest</t>
         </is>
       </c>
       <c r="D9" s="46" t="n">
@@ -4044,123 +4253,127 @@
       </c>
       <c r="E9" s="50" t="inlineStr">
         <is>
-          <t>Romorantin-Lanthenay</t>
+          <t>Pontlevoy</t>
         </is>
       </c>
       <c r="F9" s="50" t="inlineStr">
         <is>
-          <t>Mur-de-Sologne (L-Me-V) · Romorantin + La Ferté-Imbault (Ma-J-S)</t>
-        </is>
-      </c>
-      <c r="G9" s="50" t="inlineStr">
-        <is>
-          <t>Mixte selon le jour</t>
-        </is>
+          <t>Pontlevoy</t>
+        </is>
+      </c>
+      <c r="G9" s="46" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" s="46" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B10" s="50" t="inlineStr">
-        <is>
-          <t>Référent Sologne Est</t>
-        </is>
-      </c>
-      <c r="C10" s="46" t="inlineStr">
-        <is>
-          <t>Est</t>
-        </is>
-      </c>
-      <c r="D10" s="46" t="n">
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Sud-Ouest — PROD Pontlevoy / Valencisse</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Pontlevoy</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>Pontlevoy · Valencisse</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>Nord — Vendôme / Épiais</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="50" t="inlineStr">
-        <is>
-          <t>Crouy-sur-Cosson ou Lamotte-Beuvron</t>
-        </is>
-      </c>
-      <c r="F10" s="50" t="inlineStr">
-        <is>
-          <t>Crouy-sur-Cosson (L-Me-V) · Vouzon (Ma-J-S)</t>
-        </is>
-      </c>
-      <c r="G10" s="50" t="inlineStr">
-        <is>
-          <t>SAV matin / PROD après-midi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>T7</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
-        <is>
-          <t>PROD Blois agglo</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="28" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr">
-        <is>
-          <t>PROD</t>
-        </is>
+      <c r="E11" s="50" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="F11" s="50" t="inlineStr">
+        <is>
+          <t>Épiais · Vendôme</t>
+        </is>
+      </c>
+      <c r="G11" s="46" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="46" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>PROD Blois agglo</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t>PROD</t>
-        </is>
+      <c r="B12" s="50" t="inlineStr">
+        <is>
+          <t>Nord — Montoire / Cormenon</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="50" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="F12" s="50" t="inlineStr">
+        <is>
+          <t>Montoire-sur-le-Loir · Cormenon</t>
+        </is>
+      </c>
+      <c r="G12" s="46" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" s="46" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
@@ -4171,7 +4384,7 @@
       </c>
       <c r="B13" s="28" t="inlineStr">
         <is>
-          <t>PROD Nord</t>
+          <t>Nord — PROD Vendômois / Beauce</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -4189,121 +4402,399 @@
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Vendôme · Épiais · Montoire · Cormenon</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="inlineStr">
-        <is>
-          <t>PROD</t>
-        </is>
+          <t>Vendôme · Épiais</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>T10</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
-        <is>
-          <t>PROD Sologne</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
+        <is>
+          <t>Sologne Est — Crouy / Vouzon</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>Est</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="50" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson ou Lamotte-Beuvron</t>
+        </is>
+      </c>
+      <c r="F14" s="50" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson · Vouzon</t>
+        </is>
+      </c>
+      <c r="G14" s="46" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" s="46" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B15" s="50" t="inlineStr">
+        <is>
+          <t>Sologne Sud — Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>Sologne Sud</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D15" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="50" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="F15" s="50" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne · Romorantin-Lanthenay · La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="G15" s="46" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" s="46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Sologne — PROD</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Sologne Sud</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>Romorantin-Lanthenay</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
-        <is>
-          <t>Romorantin · Mur-de-Sologne · La Ferté-Imbault · Vouzon</t>
-        </is>
-      </c>
-      <c r="G14" s="28" t="inlineStr">
-        <is>
-          <t>PROD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>T11</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="inlineStr">
-        <is>
-          <t>PROD Sud-Ouest</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Sud-Ouest</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay · Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Sologne / Val de Loire — PROD</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Est</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="28" t="inlineStr">
-        <is>
-          <t>Pontlevoy</t>
-        </is>
-      </c>
-      <c r="F15" s="28" t="inlineStr">
-        <is>
-          <t>Pontlevoy · Valencisse</t>
-        </is>
-      </c>
-      <c r="G15" s="28" t="inlineStr">
-        <is>
-          <t>PROD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson ou Lamotte-Beuvron</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson · Romorantin-Lanthenay · Vouzon · Mur-de-Sologne · La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="27">
-        <f>COUNTA(A5:A15)&amp;" techniciens"</f>
-        <v/>
-      </c>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27">
-        <f>SUM(D5:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="inlineStr">
+      <c r="B18" s="27">
+        <f>COUNTA(A5:A17)&amp;" techniciens"</f>
+        <v/>
+      </c>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27">
+        <f>SUM(D5:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="27" t="inlineStr">
         <is>
           <t>12 secteurs GRDV couverts</t>
         </is>
       </c>
-      <c r="G16" s="27" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Fond orange = les 5 techniciens travaillant 6 jours. Ce sont eux qui doivent porter les secteurs du rythme Mardi-Jeudi-Samedi : sans leur samedi, aucun créneau SAV n'existe à J+1/J+2 pour un appel du jeudi ou du vendredi.</t>
-        </is>
+      <c r="G18" s="27">
+        <f>SUM(G5:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="27">
+        <f>SUM(H5:H17)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Le technicien 100 % SAV déjà en poste devient T1 sur Blois, qui concentre 34 % du volume départemental.</t>
-        </is>
-      </c>
+      <c r="A19" s="51" t="n"/>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
+      <c r="E19" s="52" t="n"/>
+      <c r="F19" s="52" t="n"/>
+      <c r="G19" s="52" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>Fond orange = les 7 techniciens à 6 jours. Ce sont eux qui portent les secteurs du rythme Mardi-Jeudi-Samedi : sans leur samedi, aucun créneau SAV n'existe à J+1/J+2 pour un appel du jeudi ou du vendredi.</t>
+        </is>
+      </c>
+      <c r="B20" s="52" t="n"/>
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="n"/>
+      <c r="G20" s="52" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="51" t="inlineStr">
+        <is>
+          <t>T1 est le technicien 100 % SAV déjà en poste, maintenu sur Blois et Valencisse comme demandé (11 km entre les deux hubs).</t>
+        </is>
+      </c>
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
+      <c r="E21" s="52" t="n"/>
+      <c r="F21" s="52" t="n"/>
+      <c r="G21" s="52" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>Effectif actuel : 11 techniciens. Ce montage en requiert 13, dont 7 à 6 jours.</t>
+        </is>
+      </c>
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="52" t="n"/>
+      <c r="D22" s="52" t="n"/>
+      <c r="E22" s="52" t="n"/>
+      <c r="F22" s="52" t="n"/>
+      <c r="G22" s="52" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="52" t="n"/>
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+      <c r="E23" s="52" t="n"/>
+      <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="52" t="n"/>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="52" t="n"/>
+      <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="52" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="52" t="n"/>
+      <c r="B26" s="52" t="n"/>
+      <c r="C26" s="52" t="n"/>
+      <c r="D26" s="52" t="n"/>
+      <c r="E26" s="52" t="n"/>
+      <c r="F26" s="52" t="n"/>
+      <c r="G26" s="52" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="52" t="n"/>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="52" t="n"/>
+      <c r="D27" s="52" t="n"/>
+      <c r="E27" s="52" t="n"/>
+      <c r="F27" s="52" t="n"/>
+      <c r="G27" s="52" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="52" t="n"/>
+      <c r="B28" s="52" t="n"/>
+      <c r="C28" s="52" t="n"/>
+      <c r="D28" s="52" t="n"/>
+      <c r="E28" s="52" t="n"/>
+      <c r="F28" s="52" t="n"/>
+      <c r="G28" s="52" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="52" t="n"/>
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="52" t="n"/>
+      <c r="D29" s="52" t="n"/>
+      <c r="E29" s="52" t="n"/>
+      <c r="F29" s="52" t="n"/>
+      <c r="G29" s="52" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="52" t="n"/>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+      <c r="E30" s="52" t="n"/>
+      <c r="F30" s="52" t="n"/>
+      <c r="G30" s="52" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="52" t="n"/>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+      <c r="E31" s="52" t="n"/>
+      <c r="F31" s="52" t="n"/>
+      <c r="G31" s="52" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="52" t="n"/>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+      <c r="E32" s="52" t="n"/>
+      <c r="F32" s="52" t="n"/>
+      <c r="G32" s="52" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="52" t="n"/>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+      <c r="E33" s="52" t="n"/>
+      <c r="F33" s="52" t="n"/>
+      <c r="G33" s="52" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="52" t="n"/>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+      <c r="E34" s="52" t="n"/>
+      <c r="F34" s="52" t="n"/>
+      <c r="G34" s="52" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="52" t="n"/>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+      <c r="E35" s="52" t="n"/>
+      <c r="F35" s="52" t="n"/>
+      <c r="G35" s="52" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="52" t="n"/>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+      <c r="E36" s="52" t="n"/>
+      <c r="F36" s="52" t="n"/>
+      <c r="G36" s="52" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="52" t="n"/>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+      <c r="E37" s="52" t="n"/>
+      <c r="F37" s="52" t="n"/>
+      <c r="G37" s="52" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="52" t="n"/>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+      <c r="E38" s="52" t="n"/>
+      <c r="F38" s="52" t="n"/>
+      <c r="G38" s="52" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="52" t="n"/>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+      <c r="E39" s="52" t="n"/>
+      <c r="F39" s="52" t="n"/>
+      <c r="G39" s="52" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="52" t="n"/>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+      <c r="E40" s="52" t="n"/>
+      <c r="F40" s="52" t="n"/>
+      <c r="G40" s="52" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4434,7 +4925,7 @@
       </c>
       <c r="O5" s="27" t="inlineStr">
         <is>
-          <t>SAV RÉEL /sem. (à saisir)</t>
+          <t>SAV réel /sem. (planning fourni)</t>
         </is>
       </c>
       <c r="P5" s="27" t="inlineStr">
@@ -4507,10 +4998,10 @@
         <v/>
       </c>
       <c r="N6" s="30" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="P6" s="12">
         <f>$O6/$M6</f>
@@ -4582,7 +5073,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P7" s="12">
         <f>$O7/$M7</f>
@@ -4651,10 +5142,10 @@
         <v/>
       </c>
       <c r="N8" s="30" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="P8" s="12">
         <f>$O8/$M8</f>
@@ -4726,7 +5217,7 @@
         <v>9</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P9" s="12">
         <f>$O9/$M9</f>
@@ -4795,10 +5286,10 @@
         <v/>
       </c>
       <c r="N10" s="30" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P10" s="12">
         <f>$O10/$M10</f>
@@ -4867,10 +5358,10 @@
         <v/>
       </c>
       <c r="N11" s="30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P11" s="12">
         <f>$O11/$M11</f>
@@ -4939,10 +5430,10 @@
         <v/>
       </c>
       <c r="N12" s="30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P12" s="12">
         <f>$O12/$M12</f>
@@ -5011,10 +5502,10 @@
         <v/>
       </c>
       <c r="N13" s="30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P13" s="12">
         <f>$O13/$M13</f>
@@ -5083,10 +5574,10 @@
         <v/>
       </c>
       <c r="N14" s="30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P14" s="12">
         <f>$O14/$M14</f>
@@ -5155,10 +5646,10 @@
         <v/>
       </c>
       <c r="N15" s="30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P15" s="12">
         <f>$O15/$M15</f>
@@ -5227,10 +5718,10 @@
         <v/>
       </c>
       <c r="N16" s="30" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16" s="12">
         <f>$O16/$M16</f>
@@ -5299,7 +5790,7 @@
         <v/>
       </c>
       <c r="N17" s="30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O17" s="10" t="n">
         <v>4</v>
